--- a/powerbi_output.xlsx
+++ b/powerbi_output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="25">
   <si>
     <t>客戶代號</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Purchase</t>
   </si>
   <si>
+    <t>Not Purchase</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -86,7 +89,7 @@
     <t>Predicted Purchase Rate (預測再購率)</t>
   </si>
   <si>
-    <t>100.00%</t>
+    <t>87.63%</t>
   </si>
 </sst>
 </file>
@@ -3370,10 +3373,10 @@
         <v>1</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3408,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3446,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3484,10 +3487,10 @@
         <v>1</v>
       </c>
       <c r="K80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3522,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3560,10 +3563,10 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3826,10 +3829,10 @@
         <v>1</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -3940,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -3978,10 +3981,10 @@
         <v>1</v>
       </c>
       <c r="K93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4054,10 +4057,10 @@
         <v>1</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4092,10 +4095,10 @@
         <v>1</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4130,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4190,15 +4193,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>97</v>
@@ -4206,23 +4209,23 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>3.11340206185567</v>
@@ -4230,7 +4233,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0.01551546391752578</v>
@@ -4238,7 +4241,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>9.402061855670103</v>
@@ -4246,7 +4249,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>5.605473154639175</v>
@@ -4254,10 +4257,10 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
